--- a/output/laminas_comunales/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -1368,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1377,527 +1377,369 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alhué</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>19.03</v>
+          <t>San Joaquín</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>14.4</v>
+          <t>San Miguel</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>12.05</v>
+          <t>San Ramón</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>12.76</v>
+          <t>Independencia</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>15.99</v>
+          <t>La Cisterna</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>10.87</v>
+          <t>Peñalolén</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conchalí</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>13.96</v>
+          <t>Providencia</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Curacaví</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>15.34</v>
+          <t>La Reina</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>14.9</v>
+          <t>Calera de Tango</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Monte</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>14.88</v>
+          <t>Colina</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estación Central</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>13.22</v>
+          <t>Santiago</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>10</v>
+          <t>Lampa</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>13.81</v>
+          <t>Pirque</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>15.75</v>
+          <t>Puente Alto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>11.25</v>
+          <t>Huechuraba</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>11.22</v>
+          <t>San Bernardo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Granja</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>14.59</v>
+          <t>Curacaví</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>17.09</v>
+          <t>María Pinto</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>La Reina</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>7.62</v>
+          <t>Cerrillos</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>9.77</v>
+          <t>Cerro Navia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>4.44</v>
+          <t>Vitacura</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>7.14</v>
+          <t>Conchalí</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>15.35</v>
+          <t>El Bosque</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>14.78</v>
+          <t>Estación Central</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Macul</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>10.18</v>
+          <t>La Florida</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maipú</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>10.95</v>
+          <t>La Granja</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>María Pinto</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>15.75</v>
+          <t>La Pintana</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Melipilla</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>19.44</v>
+          <t>Las Condes</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>5.78</v>
+          <t>Lo Barnechea</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>11.04</v>
+          <t>Lo Espejo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paine</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>18.78</v>
+          <t>Lo Prado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>14.12</v>
+          <t>Macul</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>11.59</v>
+          <t>Maipú</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>13.65</v>
+          <t>Ñuñoa</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pirque</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>10.73</v>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>4.51</v>
+          <t>Pudahuel</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>12.25</v>
+          <t>Quilicura</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>12.25</v>
+          <t>Quinta Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>11.21</v>
+          <t>Recoleta</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>12.63</v>
+          <t>Renca</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>14.7</v>
+          <t>El Monte</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Renca</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>13.64</v>
+          <t>Padre Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>13.24</v>
+          <t>Peñaflor</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>12.82</v>
+          <t>Talagante</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>11.3</v>
+          <t>Paine</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>8.06</v>
+          <t>Isla de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>San Pedro</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>16.61</v>
+          <t>Buin</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>15.21</v>
+          <t>San José de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>12.45</v>
+          <t>Tiltil</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>13.16</v>
+          <t>Melipilla</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>San Pedro</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>2.98</v>
+          <t>Alhué</t>
+        </is>
       </c>
     </row>
   </sheetData>
